--- a/02_data/SITOUREF/Type_sitous.xlsx
+++ b/02_data/SITOUREF/Type_sitous.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agencesdeleau-my.sharepoint.com/personal/vagneur_clemence_aesn_fr/Documents/Chantiers/OUTIL-016-2025_Maillage_sitous/VizMaillageSitous/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agencesdeleau.sharepoint.com/sites/AESN-Etudespressions/Shared Documents/Pressions/PANDA Pression/PANDA_Pression/02_data/SITOUREF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_A3486C562D023F4EC9102F8C74B833470CD10764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E811CDA-8F7F-4DC1-893C-FF602E9C87DB}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_A3486C562D023F4EC9102F8C74B833470CD10764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7784627C-CE0F-40FC-A031-13BF2C436839}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27840" yWindow="960" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rapport 1" sheetId="1" r:id="rId1"/>
@@ -502,7 +502,7 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -992,7 +992,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>112</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>114</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>115</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>116</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>90</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" s="1" customFormat="1" ht="19.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>61</v>
       </c>
@@ -1379,11 +1379,7 @@
   <autoFilter ref="A1:B67" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="POINT AUTOSURVEILLANCE"/>
-        <filter val="Point autosurveillance SSCL"/>
-        <filter val="Point de comptage"/>
-        <filter val="Point d'eau"/>
-        <filter val="Point prél. eaux sup."/>
+        <filter val="Site non économique"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B67">
@@ -1397,8 +1393,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0B707973A0EDF4D8C0132D38830BF56" ma:contentTypeVersion="3" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="633c736c1f52b59bab6ff2ec826f3b7e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4222387a-a7c4-4a56-bf01-5dca1ac56634" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a8c24be4bccf061f1609b4dbaef8d8d2" ns2:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0B707973A0EDF4D8C0132D38830BF56" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6fab73de96728382b95836a8b817e49f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4222387a-a7c4-4a56-bf01-5dca1ac56634" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d5a3db95c4c940e29da1a6f70bc1044" ns2:_="">
     <xsd:import namespace="4222387a-a7c4-4a56-bf01-5dca1ac56634"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -1444,8 +1449,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1534,15 +1539,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1550,13 +1546,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A262EE5-98E4-47AE-B471-E95A53198AD8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DD90B9C-227C-4862-B9F0-9356956F6F6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DD90B9C-227C-4862-B9F0-9356956F6F6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{988D646B-9AB5-4621-BCE6-73281F4F57C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69651F1D-5F2E-4A4C-82A2-CB80F6841B2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69651F1D-5F2E-4A4C-82A2-CB80F6841B2C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>